--- a/test-members-after-import.xlsx
+++ b/test-members-after-import.xlsx
@@ -1,41 +1,167 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dewkiad\Kiss Me Ranking\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D6226B5-A38D-4255-B5EC-1AF377806C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Members" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="45">
+  <si>
+    <t>export_date</t>
+  </si>
+  <si>
+    <t>export_datetime</t>
+  </si>
+  <si>
+    <t>member_id</t>
+  </si>
+  <si>
+    <t>line_user_id</t>
+  </si>
+  <si>
+    <t>display_name</t>
+  </si>
+  <si>
+    <t>first_name</t>
+  </si>
+  <si>
+    <t>last_name</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>branch_code</t>
+  </si>
+  <si>
+    <t>branch_name</t>
+  </si>
+  <si>
+    <t>total_score</t>
+  </si>
+  <si>
+    <t>available_points</t>
+  </si>
+  <si>
+    <t>lifetime_redeemed_points</t>
+  </si>
+  <si>
+    <t>tier_name</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>is_blocked</t>
+  </si>
+  <si>
+    <t>registered_at</t>
+  </si>
+  <si>
+    <t>last_login_at</t>
+  </si>
+  <si>
+    <t>last_activity_at</t>
+  </si>
+  <si>
+    <t>updated_at</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>2026-04-18T10:12:55.303Z</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>codex-avatar-test-1776331355</t>
+  </si>
+  <si>
+    <t>Codex Avatar Test 1776331355 TEMP-TEST</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Member</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>2026-04-16T02:22:37.323Z</t>
+  </si>
+  <si>
+    <t>1970-01-01T00:00:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-04-18T03:12:42.451Z</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>codex-avatar-test-1776331199</t>
+  </si>
+  <si>
+    <t>Codex Avatar Test 1776331199</t>
+  </si>
+  <si>
+    <t>2026-04-16T02:20:00.680Z</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>codex-avatar-test-1776330979</t>
+  </si>
+  <si>
+    <t>Codex Avatar Test 1776330979</t>
+  </si>
+  <si>
+    <t>2026-04-16T02:16:21.448Z</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>U9e2de166944ab1f2bfa48f7a16ef95cd</t>
+  </si>
+  <si>
+    <t>Dew💦</t>
+  </si>
+  <si>
+    <t>2026-04-16T01:14:37.635Z</t>
+  </si>
+  <si>
+    <t>2026-04-15T17:00:00.000Z</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +191,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,107 +530,111 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="11.75" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>export_date</v>
-      </c>
-      <c r="B1" t="str">
-        <v>export_datetime</v>
-      </c>
-      <c r="C1" t="str">
-        <v>member_id</v>
-      </c>
-      <c r="D1" t="str">
-        <v>line_user_id</v>
-      </c>
-      <c r="E1" t="str">
-        <v>display_name</v>
-      </c>
-      <c r="F1" t="str">
-        <v>first_name</v>
-      </c>
-      <c r="G1" t="str">
-        <v>last_name</v>
-      </c>
-      <c r="H1" t="str">
-        <v>phone</v>
-      </c>
-      <c r="I1" t="str">
-        <v>email</v>
-      </c>
-      <c r="J1" t="str">
-        <v>branch_code</v>
-      </c>
-      <c r="K1" t="str">
-        <v>branch_name</v>
-      </c>
-      <c r="L1" t="str">
-        <v>total_score</v>
-      </c>
-      <c r="M1" t="str">
-        <v>available_points</v>
-      </c>
-      <c r="N1" t="str">
-        <v>lifetime_redeemed_points</v>
-      </c>
-      <c r="O1" t="str">
-        <v>tier_name</v>
-      </c>
-      <c r="P1" t="str">
-        <v>status</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>is_blocked</v>
-      </c>
-      <c r="R1" t="str">
-        <v>registered_at</v>
-      </c>
-      <c r="S1" t="str">
-        <v>last_login_at</v>
-      </c>
-      <c r="T1" t="str">
-        <v>last_activity_at</v>
-      </c>
-      <c r="U1" t="str">
-        <v>updated_at</v>
+    <row r="1" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>2026-04-18</v>
-      </c>
-      <c r="B2" t="str">
-        <v>2026-04-18T10:12:55.303Z</v>
-      </c>
-      <c r="C2" t="str">
-        <v>5</v>
-      </c>
-      <c r="D2" t="str">
-        <v>codex-avatar-test-1776331355</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Codex Avatar Test 1776331355 TEMP-TEST</v>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
-        <v/>
-      </c>
-      <c r="J2" t="str">
-        <v/>
-      </c>
-      <c r="K2" t="str">
-        <v/>
+    <row r="2" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" t="s">
+        <v>26</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -507,61 +645,61 @@
       <c r="N2">
         <v>0</v>
       </c>
-      <c r="O2" t="str">
-        <v>Member</v>
-      </c>
-      <c r="P2" t="str">
-        <v>active</v>
+      <c r="O2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" t="s">
+        <v>28</v>
       </c>
       <c r="Q2" t="b">
         <v>0</v>
       </c>
-      <c r="R2" t="str">
-        <v>2026-04-16T02:22:37.323Z</v>
-      </c>
-      <c r="S2" t="str">
-        <v/>
-      </c>
-      <c r="T2" t="str">
-        <v>1970-01-01T00:00:00.000Z</v>
-      </c>
-      <c r="U2" t="str">
-        <v>2026-04-18T03:12:42.451Z</v>
+      <c r="R2" t="s">
+        <v>29</v>
+      </c>
+      <c r="S2" t="s">
+        <v>26</v>
+      </c>
+      <c r="T2" t="s">
+        <v>30</v>
+      </c>
+      <c r="U2" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2026-04-18</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-04-18T10:12:55.303Z</v>
-      </c>
-      <c r="C3" t="str">
-        <v>4</v>
-      </c>
-      <c r="D3" t="str">
-        <v>codex-avatar-test-1776331199</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Codex Avatar Test 1776331199</v>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v/>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
+    <row r="3" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" t="s">
+        <v>26</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -572,61 +710,61 @@
       <c r="N3">
         <v>0</v>
       </c>
-      <c r="O3" t="str">
-        <v>Member</v>
-      </c>
-      <c r="P3" t="str">
-        <v>active</v>
+      <c r="O3" t="s">
+        <v>27</v>
+      </c>
+      <c r="P3" t="s">
+        <v>28</v>
       </c>
       <c r="Q3" t="b">
         <v>0</v>
       </c>
-      <c r="R3" t="str">
-        <v>2026-04-16T02:20:00.680Z</v>
-      </c>
-      <c r="S3" t="str">
-        <v/>
-      </c>
-      <c r="T3" t="str">
-        <v>1970-01-01T00:00:00.000Z</v>
-      </c>
-      <c r="U3" t="str">
-        <v>2026-04-18T03:12:42.451Z</v>
+      <c r="R3" t="s">
+        <v>35</v>
+      </c>
+      <c r="S3" t="s">
+        <v>26</v>
+      </c>
+      <c r="T3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U3" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>2026-04-18</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-04-18T10:12:55.303Z</v>
-      </c>
-      <c r="C4" t="str">
-        <v>3</v>
-      </c>
-      <c r="D4" t="str">
-        <v>codex-avatar-test-1776330979</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Codex Avatar Test 1776330979</v>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v/>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
+    <row r="4" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" t="s">
+        <v>26</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -637,61 +775,61 @@
       <c r="N4">
         <v>0</v>
       </c>
-      <c r="O4" t="str">
-        <v>Member</v>
-      </c>
-      <c r="P4" t="str">
-        <v>active</v>
+      <c r="O4" t="s">
+        <v>27</v>
+      </c>
+      <c r="P4" t="s">
+        <v>28</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
-      <c r="R4" t="str">
-        <v>2026-04-16T02:16:21.448Z</v>
-      </c>
-      <c r="S4" t="str">
-        <v/>
-      </c>
-      <c r="T4" t="str">
-        <v>1970-01-01T00:00:00.000Z</v>
-      </c>
-      <c r="U4" t="str">
-        <v>2026-04-18T03:12:42.451Z</v>
+      <c r="R4" t="s">
+        <v>39</v>
+      </c>
+      <c r="S4" t="s">
+        <v>26</v>
+      </c>
+      <c r="T4" t="s">
+        <v>30</v>
+      </c>
+      <c r="U4" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2026-04-18</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-04-18T10:12:55.303Z</v>
-      </c>
-      <c r="C5" t="str">
-        <v>1</v>
-      </c>
-      <c r="D5" t="str">
-        <v>U9e2de166944ab1f2bfa48f7a16ef95cd</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Dew💦</v>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v/>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
+    <row r="5" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" t="s">
+        <v>26</v>
       </c>
       <c r="L5">
         <v>3</v>
@@ -702,31 +840,32 @@
       <c r="N5">
         <v>0</v>
       </c>
-      <c r="O5" t="str">
-        <v>Member</v>
-      </c>
-      <c r="P5" t="str">
-        <v>active</v>
+      <c r="O5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P5" t="s">
+        <v>28</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
       </c>
-      <c r="R5" t="str">
-        <v>2026-04-16T01:14:37.635Z</v>
-      </c>
-      <c r="S5" t="str">
-        <v/>
-      </c>
-      <c r="T5" t="str">
-        <v>2026-04-15T17:00:00.000Z</v>
-      </c>
-      <c r="U5" t="str">
-        <v>2026-04-18T03:12:42.451Z</v>
+      <c r="R5" t="s">
+        <v>43</v>
+      </c>
+      <c r="S5" t="s">
+        <v>26</v>
+      </c>
+      <c r="T5" t="s">
+        <v>44</v>
+      </c>
+      <c r="U5" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U5"/>
+    <ignoredError sqref="A1:U5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>